--- a/artfynd/A 39692-2024 artfynd.xlsx
+++ b/artfynd/A 39692-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819424</v>
+        <v>119819420</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690597</v>
+        <v>690715</v>
       </c>
       <c r="R3" t="n">
-        <v>7232754</v>
+        <v>7232772</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819419</v>
+        <v>119819423</v>
       </c>
       <c r="B4" t="n">
-        <v>96868</v>
+        <v>91884</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690634</v>
+        <v>690597</v>
       </c>
       <c r="R4" t="n">
-        <v>7233057</v>
+        <v>7232755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819423</v>
+        <v>119819424</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1166,7 +1166,7 @@
         <v>690597</v>
       </c>
       <c r="R6" t="n">
-        <v>7232755</v>
+        <v>7232754</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819420</v>
+        <v>119819419</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>96868</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690715</v>
+        <v>690634</v>
       </c>
       <c r="R7" t="n">
-        <v>7232772</v>
+        <v>7233057</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 39692-2024 artfynd.xlsx
+++ b/artfynd/A 39692-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819420</v>
+        <v>119819419</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>96868</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690715</v>
+        <v>690634</v>
       </c>
       <c r="R3" t="n">
-        <v>7232772</v>
+        <v>7233057</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819417</v>
+        <v>119819424</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690635</v>
+        <v>690597</v>
       </c>
       <c r="R5" t="n">
-        <v>7233110</v>
+        <v>7232754</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819424</v>
+        <v>119819417</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690597</v>
+        <v>690635</v>
       </c>
       <c r="R6" t="n">
-        <v>7232754</v>
+        <v>7233110</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819419</v>
+        <v>119819420</v>
       </c>
       <c r="B7" t="n">
-        <v>96868</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690634</v>
+        <v>690715</v>
       </c>
       <c r="R7" t="n">
-        <v>7233057</v>
+        <v>7232772</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 39692-2024 artfynd.xlsx
+++ b/artfynd/A 39692-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819422</v>
+        <v>119819419</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690675</v>
+        <v>690634</v>
       </c>
       <c r="R2" t="n">
-        <v>7232751</v>
+        <v>7233057</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819419</v>
+        <v>119819420</v>
       </c>
       <c r="B3" t="n">
-        <v>96868</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690634</v>
+        <v>690715</v>
       </c>
       <c r="R3" t="n">
-        <v>7233057</v>
+        <v>7232772</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819423</v>
+        <v>119819424</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,7 +944,7 @@
         <v>690597</v>
       </c>
       <c r="R4" t="n">
-        <v>7232755</v>
+        <v>7232754</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819424</v>
+        <v>119819417</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690597</v>
+        <v>690635</v>
       </c>
       <c r="R5" t="n">
-        <v>7232754</v>
+        <v>7233110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819417</v>
+        <v>119819423</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690635</v>
+        <v>690597</v>
       </c>
       <c r="R6" t="n">
-        <v>7233110</v>
+        <v>7232755</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819420</v>
+        <v>119819422</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690715</v>
+        <v>690675</v>
       </c>
       <c r="R7" t="n">
-        <v>7232772</v>
+        <v>7232751</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 39692-2024 artfynd.xlsx
+++ b/artfynd/A 39692-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119819419</v>
       </c>
       <c r="B2" t="n">
-        <v>96868</v>
+        <v>96891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819420</v>
+        <v>119819424</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690715</v>
+        <v>690597</v>
       </c>
       <c r="R3" t="n">
-        <v>7232772</v>
+        <v>7232754</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819424</v>
+        <v>119819422</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690597</v>
+        <v>690675</v>
       </c>
       <c r="R4" t="n">
-        <v>7232754</v>
+        <v>7232751</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819417</v>
+        <v>119819423</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690635</v>
+        <v>690597</v>
       </c>
       <c r="R5" t="n">
-        <v>7233110</v>
+        <v>7232755</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819423</v>
+        <v>119819420</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>91870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690597</v>
+        <v>690715</v>
       </c>
       <c r="R6" t="n">
-        <v>7232755</v>
+        <v>7232772</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819422</v>
+        <v>119819417</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690675</v>
+        <v>690635</v>
       </c>
       <c r="R7" t="n">
-        <v>7232751</v>
+        <v>7233110</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 39692-2024 artfynd.xlsx
+++ b/artfynd/A 39692-2024 artfynd.xlsx
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819420</v>
+        <v>119819417</v>
       </c>
       <c r="B6" t="n">
         <v>91870</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690715</v>
+        <v>690635</v>
       </c>
       <c r="R6" t="n">
-        <v>7232772</v>
+        <v>7233110</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819417</v>
+        <v>119819420</v>
       </c>
       <c r="B7" t="n">
         <v>91870</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690635</v>
+        <v>690715</v>
       </c>
       <c r="R7" t="n">
-        <v>7233110</v>
+        <v>7232772</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 39692-2024 artfynd.xlsx
+++ b/artfynd/A 39692-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819419</v>
+        <v>119819422</v>
       </c>
       <c r="B2" t="n">
-        <v>96891</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690634</v>
+        <v>690675</v>
       </c>
       <c r="R2" t="n">
-        <v>7233057</v>
+        <v>7232751</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819424</v>
+        <v>119819417</v>
       </c>
       <c r="B3" t="n">
-        <v>91850</v>
+        <v>91870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690597</v>
+        <v>690635</v>
       </c>
       <c r="R3" t="n">
-        <v>7232754</v>
+        <v>7233110</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819422</v>
+        <v>119819423</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690675</v>
+        <v>690597</v>
       </c>
       <c r="R4" t="n">
-        <v>7232751</v>
+        <v>7232755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819423</v>
+        <v>119819424</v>
       </c>
       <c r="B5" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,7 +1055,7 @@
         <v>690597</v>
       </c>
       <c r="R5" t="n">
-        <v>7232755</v>
+        <v>7232754</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819417</v>
+        <v>119819419</v>
       </c>
       <c r="B6" t="n">
-        <v>91870</v>
+        <v>96891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690635</v>
+        <v>690634</v>
       </c>
       <c r="R6" t="n">
-        <v>7233110</v>
+        <v>7233057</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 39692-2024 artfynd.xlsx
+++ b/artfynd/A 39692-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819422</v>
+        <v>119819419</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>96891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690675</v>
+        <v>690634</v>
       </c>
       <c r="R2" t="n">
-        <v>7232751</v>
+        <v>7233057</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819417</v>
+        <v>119819424</v>
       </c>
       <c r="B3" t="n">
-        <v>91870</v>
+        <v>91850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690635</v>
+        <v>690597</v>
       </c>
       <c r="R3" t="n">
-        <v>7233110</v>
+        <v>7232754</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819423</v>
+        <v>119819420</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>91870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690597</v>
+        <v>690715</v>
       </c>
       <c r="R4" t="n">
-        <v>7232755</v>
+        <v>7232772</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819424</v>
+        <v>119819422</v>
       </c>
       <c r="B5" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690597</v>
+        <v>690675</v>
       </c>
       <c r="R5" t="n">
-        <v>7232754</v>
+        <v>7232751</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819419</v>
+        <v>119819417</v>
       </c>
       <c r="B6" t="n">
-        <v>96891</v>
+        <v>91870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690634</v>
+        <v>690635</v>
       </c>
       <c r="R6" t="n">
-        <v>7233057</v>
+        <v>7233110</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819420</v>
+        <v>119819423</v>
       </c>
       <c r="B7" t="n">
-        <v>91870</v>
+        <v>91902</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690715</v>
+        <v>690597</v>
       </c>
       <c r="R7" t="n">
-        <v>7232772</v>
+        <v>7232755</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 39692-2024 artfynd.xlsx
+++ b/artfynd/A 39692-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819419</v>
+        <v>119819424</v>
       </c>
       <c r="B2" t="n">
-        <v>96891</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690634</v>
+        <v>690597</v>
       </c>
       <c r="R2" t="n">
-        <v>7233057</v>
+        <v>7232754</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819424</v>
+        <v>119819422</v>
       </c>
       <c r="B3" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690597</v>
+        <v>690675</v>
       </c>
       <c r="R3" t="n">
-        <v>7232754</v>
+        <v>7232751</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,19 +887,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819420</v>
+        <v>119819417</v>
       </c>
       <c r="B4" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690715</v>
+        <v>690635</v>
       </c>
       <c r="R4" t="n">
-        <v>7232772</v>
+        <v>7233110</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819422</v>
+        <v>119819420</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690675</v>
+        <v>690715</v>
       </c>
       <c r="R5" t="n">
-        <v>7232751</v>
+        <v>7232772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819417</v>
+        <v>119819419</v>
       </c>
       <c r="B6" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690635</v>
+        <v>690634</v>
       </c>
       <c r="R6" t="n">
-        <v>7233110</v>
+        <v>7233057</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,117 +1202,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>119819423</v>
-      </c>
-      <c r="B7" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Näsliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>690597</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7232755</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Malå</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Malå</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39692-2024 artfynd.xlsx
+++ b/artfynd/A 39692-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819422</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819417</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819420</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819419</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>